--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OREGON_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OREGON_2014.xlsx
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C224">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C233">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C653">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C771">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C810">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C811">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C817">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1281">
